--- a/data/餐线消费数据-June.xlsx
+++ b/data/餐线消费数据-June.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aidan/Documents/GitHub/FoodBot/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3C34B3-B6A0-7C4E-8420-41695D21DAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7FC763-B8DD-7A4A-ACF7-4FF103FB9014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18480" yWindow="9740" windowWidth="19420" windowHeight="10300" tabRatio="862" firstSheet="2" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="600" yWindow="8620" windowWidth="19420" windowHeight="10300" tabRatio="862" firstSheet="2" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jun 3" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2871" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3285" uniqueCount="13">
   <si>
     <t>会员编号</t>
   </si>
@@ -12507,7 +12507,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B409"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -12516,6 +12516,3270 @@
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>3999</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>3999</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>4437</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4437</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5786</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5786</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>5959</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>5959</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>5959</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>5162</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>5162</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>6236</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>6236</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>5074</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>5074</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>5074</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>5096</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>5096</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>5744</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>5744</v>
+      </c>
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>111228</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>111228</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>2649</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>4001</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4012</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4015</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4021</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4064</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4171</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4396</v>
+      </c>
+      <c r="B31" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4412</v>
+      </c>
+      <c r="B32" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4427</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>4492</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>4501</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>4501</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>4528</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>4606</v>
+      </c>
+      <c r="B38" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>4704</v>
+      </c>
+      <c r="B39" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>4722</v>
+      </c>
+      <c r="B40" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>4725</v>
+      </c>
+      <c r="B41" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>4738</v>
+      </c>
+      <c r="B42" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>4741</v>
+      </c>
+      <c r="B43" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>4790</v>
+      </c>
+      <c r="B44" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>4812</v>
+      </c>
+      <c r="B45" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>4815</v>
+      </c>
+      <c r="B46" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>4879</v>
+      </c>
+      <c r="B47" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>4983</v>
+      </c>
+      <c r="B48" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>5002</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>5074</v>
+      </c>
+      <c r="B50" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>5103</v>
+      </c>
+      <c r="B51" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>5119</v>
+      </c>
+      <c r="B52" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>5132</v>
+      </c>
+      <c r="B53" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>5136</v>
+      </c>
+      <c r="B54" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>5193</v>
+      </c>
+      <c r="B55" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>5321</v>
+      </c>
+      <c r="B56" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>5359</v>
+      </c>
+      <c r="B57" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>5374</v>
+      </c>
+      <c r="B58" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>5388</v>
+      </c>
+      <c r="B59" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>5395</v>
+      </c>
+      <c r="B60" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>5408</v>
+      </c>
+      <c r="B61" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>5421</v>
+      </c>
+      <c r="B62" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>5451</v>
+      </c>
+      <c r="B63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>5484</v>
+      </c>
+      <c r="B64" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>5490</v>
+      </c>
+      <c r="B65" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>5532</v>
+      </c>
+      <c r="B66" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>5554</v>
+      </c>
+      <c r="B67" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>5561</v>
+      </c>
+      <c r="B68" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>5622</v>
+      </c>
+      <c r="B69" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>5712</v>
+      </c>
+      <c r="B70" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>5938</v>
+      </c>
+      <c r="B71" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>5939</v>
+      </c>
+      <c r="B72" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>5941</v>
+      </c>
+      <c r="B73" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>6239</v>
+      </c>
+      <c r="B74" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>6240</v>
+      </c>
+      <c r="B75" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>6246</v>
+      </c>
+      <c r="B76" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>6273</v>
+      </c>
+      <c r="B77" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>6279</v>
+      </c>
+      <c r="B78" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>6302</v>
+      </c>
+      <c r="B79" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>6303</v>
+      </c>
+      <c r="B80" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>6320</v>
+      </c>
+      <c r="B81" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>6325</v>
+      </c>
+      <c r="B82" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>6352</v>
+      </c>
+      <c r="B83" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>6522</v>
+      </c>
+      <c r="B84" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>6545</v>
+      </c>
+      <c r="B85" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>6548</v>
+      </c>
+      <c r="B86" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>6559</v>
+      </c>
+      <c r="B87" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>6568</v>
+      </c>
+      <c r="B88" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>11402</v>
+      </c>
+      <c r="B89" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>11945</v>
+      </c>
+      <c r="B90" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>12514</v>
+      </c>
+      <c r="B91" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>12678</v>
+      </c>
+      <c r="B92" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>12753</v>
+      </c>
+      <c r="B93" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>12843</v>
+      </c>
+      <c r="B94" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>12852</v>
+      </c>
+      <c r="B95" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>12853</v>
+      </c>
+      <c r="B96" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>12880</v>
+      </c>
+      <c r="B97" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>12896</v>
+      </c>
+      <c r="B98" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>111150</v>
+      </c>
+      <c r="B99" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>111151</v>
+      </c>
+      <c r="B100" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>111204</v>
+      </c>
+      <c r="B101" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>111233</v>
+      </c>
+      <c r="B102" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>111233</v>
+      </c>
+      <c r="B103" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>111250</v>
+      </c>
+      <c r="B104" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>111254</v>
+      </c>
+      <c r="B105" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>111295</v>
+      </c>
+      <c r="B106" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>111348</v>
+      </c>
+      <c r="B107" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>111432</v>
+      </c>
+      <c r="B108" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>111464</v>
+      </c>
+      <c r="B109" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>111471</v>
+      </c>
+      <c r="B110" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>111559</v>
+      </c>
+      <c r="B111" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>111583</v>
+      </c>
+      <c r="B112" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113">
+        <v>111624</v>
+      </c>
+      <c r="B113" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114">
+        <v>111649</v>
+      </c>
+      <c r="B114" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>111667</v>
+      </c>
+      <c r="B115" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>111692</v>
+      </c>
+      <c r="B116" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>111692</v>
+      </c>
+      <c r="B117" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>111702</v>
+      </c>
+      <c r="B118" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119">
+        <v>111907</v>
+      </c>
+      <c r="B119" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>3070</v>
+      </c>
+      <c r="B120" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>3504</v>
+      </c>
+      <c r="B121" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>4171</v>
+      </c>
+      <c r="B122" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>4171</v>
+      </c>
+      <c r="B123" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>4382</v>
+      </c>
+      <c r="B124" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>4419</v>
+      </c>
+      <c r="B125" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>4432</v>
+      </c>
+      <c r="B126" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>4511</v>
+      </c>
+      <c r="B127" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A128">
+        <v>4527</v>
+      </c>
+      <c r="B128" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129">
+        <v>4529</v>
+      </c>
+      <c r="B129" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>4696</v>
+      </c>
+      <c r="B130" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>4791</v>
+      </c>
+      <c r="B131" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132">
+        <v>4801</v>
+      </c>
+      <c r="B132" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133">
+        <v>5046</v>
+      </c>
+      <c r="B133" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134">
+        <v>5163</v>
+      </c>
+      <c r="B134" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135">
+        <v>5233</v>
+      </c>
+      <c r="B135" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136">
+        <v>5247</v>
+      </c>
+      <c r="B136" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137">
+        <v>5262</v>
+      </c>
+      <c r="B137" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A138">
+        <v>5275</v>
+      </c>
+      <c r="B138" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A139">
+        <v>5436</v>
+      </c>
+      <c r="B139" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A140">
+        <v>5631</v>
+      </c>
+      <c r="B140" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A141">
+        <v>5637</v>
+      </c>
+      <c r="B141" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A142">
+        <v>5726</v>
+      </c>
+      <c r="B142" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A143">
+        <v>5817</v>
+      </c>
+      <c r="B143" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A144">
+        <v>5951</v>
+      </c>
+      <c r="B144" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145">
+        <v>5955</v>
+      </c>
+      <c r="B145" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146">
+        <v>5977</v>
+      </c>
+      <c r="B146" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147">
+        <v>6278</v>
+      </c>
+      <c r="B147" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148">
+        <v>6302</v>
+      </c>
+      <c r="B148" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149">
+        <v>6303</v>
+      </c>
+      <c r="B149" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>6329</v>
+      </c>
+      <c r="B150" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151">
+        <v>6411</v>
+      </c>
+      <c r="B151" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152">
+        <v>6517</v>
+      </c>
+      <c r="B152" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153">
+        <v>6564</v>
+      </c>
+      <c r="B153" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>8</v>
+      </c>
+      <c r="B154" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A155">
+        <v>11851</v>
+      </c>
+      <c r="B155" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A156">
+        <v>11945</v>
+      </c>
+      <c r="B156" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <v>12811</v>
+      </c>
+      <c r="B157" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A158">
+        <v>12882</v>
+      </c>
+      <c r="B158" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>12890</v>
+      </c>
+      <c r="B159" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>111152</v>
+      </c>
+      <c r="B160" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A161">
+        <v>111233</v>
+      </c>
+      <c r="B161" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>111254</v>
+      </c>
+      <c r="B162" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>111273</v>
+      </c>
+      <c r="B163" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>111331</v>
+      </c>
+      <c r="B164" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>111341</v>
+      </c>
+      <c r="B165" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>111609</v>
+      </c>
+      <c r="B166" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A167">
+        <v>3698</v>
+      </c>
+      <c r="B167" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>4052</v>
+      </c>
+      <c r="B168" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>4053</v>
+      </c>
+      <c r="B169" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>4059</v>
+      </c>
+      <c r="B170" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>4397</v>
+      </c>
+      <c r="B171" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>4419</v>
+      </c>
+      <c r="B172" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>4423</v>
+      </c>
+      <c r="B173" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>4435</v>
+      </c>
+      <c r="B174" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>4435</v>
+      </c>
+      <c r="B175" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>4435</v>
+      </c>
+      <c r="B176" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>4435</v>
+      </c>
+      <c r="B177" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A178">
+        <v>4435</v>
+      </c>
+      <c r="B178" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A179">
+        <v>4450</v>
+      </c>
+      <c r="B179" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>4455</v>
+      </c>
+      <c r="B180" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A181">
+        <v>4673</v>
+      </c>
+      <c r="B181" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A182">
+        <v>4702</v>
+      </c>
+      <c r="B182" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>4706</v>
+      </c>
+      <c r="B183" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A184">
+        <v>4749</v>
+      </c>
+      <c r="B184" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>4777</v>
+      </c>
+      <c r="B185" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>4812</v>
+      </c>
+      <c r="B186" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A187">
+        <v>4812</v>
+      </c>
+      <c r="B187" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A188">
+        <v>4923</v>
+      </c>
+      <c r="B188" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A189">
+        <v>4973</v>
+      </c>
+      <c r="B189" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A190">
+        <v>4976</v>
+      </c>
+      <c r="B190" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A191">
+        <v>5032</v>
+      </c>
+      <c r="B191" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A192">
+        <v>5103</v>
+      </c>
+      <c r="B192" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A193">
+        <v>5138</v>
+      </c>
+      <c r="B193" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A194">
+        <v>5167</v>
+      </c>
+      <c r="B194" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A195">
+        <v>5179</v>
+      </c>
+      <c r="B195" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A196">
+        <v>5179</v>
+      </c>
+      <c r="B196" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A197">
+        <v>5179</v>
+      </c>
+      <c r="B197" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A198">
+        <v>5179</v>
+      </c>
+      <c r="B198" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A199">
+        <v>5179</v>
+      </c>
+      <c r="B199" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A200">
+        <v>5179</v>
+      </c>
+      <c r="B200" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A201">
+        <v>5179</v>
+      </c>
+      <c r="B201" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A202">
+        <v>5179</v>
+      </c>
+      <c r="B202" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A203">
+        <v>5179</v>
+      </c>
+      <c r="B203" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A204">
+        <v>5179</v>
+      </c>
+      <c r="B204" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A205">
+        <v>5179</v>
+      </c>
+      <c r="B205" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A206">
+        <v>5179</v>
+      </c>
+      <c r="B206" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A207">
+        <v>5213</v>
+      </c>
+      <c r="B207" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A208">
+        <v>5233</v>
+      </c>
+      <c r="B208" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A209">
+        <v>5339</v>
+      </c>
+      <c r="B209" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A210">
+        <v>5447</v>
+      </c>
+      <c r="B210" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A211" t="s">
+        <v>8</v>
+      </c>
+      <c r="B211" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
+        <v>8</v>
+      </c>
+      <c r="B212" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>8</v>
+      </c>
+      <c r="B213" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A214">
+        <v>5815</v>
+      </c>
+      <c r="B214" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A215">
+        <v>5939</v>
+      </c>
+      <c r="B215" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A216">
+        <v>5939</v>
+      </c>
+      <c r="B216" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A217">
+        <v>5939</v>
+      </c>
+      <c r="B217" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A218">
+        <v>5939</v>
+      </c>
+      <c r="B218" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A219">
+        <v>5939</v>
+      </c>
+      <c r="B219" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A220">
+        <v>5939</v>
+      </c>
+      <c r="B220" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A221">
+        <v>5948</v>
+      </c>
+      <c r="B221" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A222">
+        <v>5949</v>
+      </c>
+      <c r="B222" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A223">
+        <v>5956</v>
+      </c>
+      <c r="B223" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A224">
+        <v>5987</v>
+      </c>
+      <c r="B224" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A225">
+        <v>6006</v>
+      </c>
+      <c r="B225" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A226">
+        <v>6060</v>
+      </c>
+      <c r="B226" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A227">
+        <v>6239</v>
+      </c>
+      <c r="B227" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A228">
+        <v>6243</v>
+      </c>
+      <c r="B228" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A229">
+        <v>6271</v>
+      </c>
+      <c r="B229" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A230">
+        <v>6308</v>
+      </c>
+      <c r="B230" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A231">
+        <v>6311</v>
+      </c>
+      <c r="B231" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A232">
+        <v>6315</v>
+      </c>
+      <c r="B232" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A233">
+        <v>6324</v>
+      </c>
+      <c r="B233" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A234">
+        <v>6579</v>
+      </c>
+      <c r="B234" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A235">
+        <v>12435</v>
+      </c>
+      <c r="B235" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A236">
+        <v>12459</v>
+      </c>
+      <c r="B236" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A237">
+        <v>12506</v>
+      </c>
+      <c r="B237" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A238">
+        <v>12528</v>
+      </c>
+      <c r="B238" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A239">
+        <v>12798</v>
+      </c>
+      <c r="B239" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A240">
+        <v>12805</v>
+      </c>
+      <c r="B240" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A241">
+        <v>12824</v>
+      </c>
+      <c r="B241" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A242">
+        <v>12832</v>
+      </c>
+      <c r="B242" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A243">
+        <v>111133</v>
+      </c>
+      <c r="B243" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A244">
+        <v>111192</v>
+      </c>
+      <c r="B244" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A245">
+        <v>111229</v>
+      </c>
+      <c r="B245" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A246">
+        <v>111232</v>
+      </c>
+      <c r="B246" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A247">
+        <v>111234</v>
+      </c>
+      <c r="B247" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A248">
+        <v>111235</v>
+      </c>
+      <c r="B248" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A249">
+        <v>111242</v>
+      </c>
+      <c r="B249" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A250">
+        <v>111253</v>
+      </c>
+      <c r="B250" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A251">
+        <v>111297</v>
+      </c>
+      <c r="B251" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A252">
+        <v>111317</v>
+      </c>
+      <c r="B252" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A253">
+        <v>111461</v>
+      </c>
+      <c r="B253" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A254">
+        <v>111462</v>
+      </c>
+      <c r="B254" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A255">
+        <v>111495</v>
+      </c>
+      <c r="B255" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A256">
+        <v>111616</v>
+      </c>
+      <c r="B256" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A257">
+        <v>111646</v>
+      </c>
+      <c r="B257" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A258">
+        <v>111653</v>
+      </c>
+      <c r="B258" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A259">
+        <v>111720</v>
+      </c>
+      <c r="B259" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A260">
+        <v>3461</v>
+      </c>
+      <c r="B260" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A261">
+        <v>4385</v>
+      </c>
+      <c r="B261" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A262">
+        <v>4444</v>
+      </c>
+      <c r="B262" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A263">
+        <v>4596</v>
+      </c>
+      <c r="B263" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A264">
+        <v>4674</v>
+      </c>
+      <c r="B264" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A265">
+        <v>4719</v>
+      </c>
+      <c r="B265" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A266">
+        <v>4725</v>
+      </c>
+      <c r="B266" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A267">
+        <v>5179</v>
+      </c>
+      <c r="B267" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A268">
+        <v>5210</v>
+      </c>
+      <c r="B268" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A269">
+        <v>5243</v>
+      </c>
+      <c r="B269" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A270">
+        <v>5252</v>
+      </c>
+      <c r="B270" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A271">
+        <v>5259</v>
+      </c>
+      <c r="B271" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A272">
+        <v>5462</v>
+      </c>
+      <c r="B272" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A273">
+        <v>5800</v>
+      </c>
+      <c r="B273" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A274">
+        <v>5818</v>
+      </c>
+      <c r="B274" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A275">
+        <v>5999</v>
+      </c>
+      <c r="B275" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A276">
+        <v>6235</v>
+      </c>
+      <c r="B276" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A277">
+        <v>6240</v>
+      </c>
+      <c r="B277" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A278">
+        <v>6316</v>
+      </c>
+      <c r="B278" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A279">
+        <v>6362</v>
+      </c>
+      <c r="B279" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A280">
+        <v>6394</v>
+      </c>
+      <c r="B280" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A281">
+        <v>6558</v>
+      </c>
+      <c r="B281" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A282">
+        <v>12296</v>
+      </c>
+      <c r="B282" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A283">
+        <v>12497</v>
+      </c>
+      <c r="B283" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A284">
+        <v>12524</v>
+      </c>
+      <c r="B284" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A285">
+        <v>12679</v>
+      </c>
+      <c r="B285" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A286" t="s">
+        <v>8</v>
+      </c>
+      <c r="B286" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A287">
+        <v>111119</v>
+      </c>
+      <c r="B287" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A288">
+        <v>111136</v>
+      </c>
+      <c r="B288" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A289">
+        <v>111249</v>
+      </c>
+      <c r="B289" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A290">
+        <v>111433</v>
+      </c>
+      <c r="B290" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A291">
+        <v>111575</v>
+      </c>
+      <c r="B291" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A292">
+        <v>2676</v>
+      </c>
+      <c r="B292" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A293">
+        <v>5303</v>
+      </c>
+      <c r="B293" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A294">
+        <v>5632</v>
+      </c>
+      <c r="B294" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A295">
+        <v>12899</v>
+      </c>
+      <c r="B295" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A296">
+        <v>111120</v>
+      </c>
+      <c r="B296" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A297">
+        <v>111142</v>
+      </c>
+      <c r="B297" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A298">
+        <v>111582</v>
+      </c>
+      <c r="B298" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A299">
+        <v>111692</v>
+      </c>
+      <c r="B299" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A300">
+        <v>4798</v>
+      </c>
+      <c r="B300" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A301">
+        <v>4861</v>
+      </c>
+      <c r="B301" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A302">
+        <v>5017</v>
+      </c>
+      <c r="B302" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A303">
+        <v>5341</v>
+      </c>
+      <c r="B303" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A304">
+        <v>5378</v>
+      </c>
+      <c r="B304" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A305">
+        <v>5410</v>
+      </c>
+      <c r="B305" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A306">
+        <v>6252</v>
+      </c>
+      <c r="B306" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A307">
+        <v>6365</v>
+      </c>
+      <c r="B307" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A308">
+        <v>12388</v>
+      </c>
+      <c r="B308" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A309">
+        <v>111205</v>
+      </c>
+      <c r="B309" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A310">
+        <v>6325</v>
+      </c>
+      <c r="B310" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A311">
+        <v>12691</v>
+      </c>
+      <c r="B311" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A312">
+        <v>12811</v>
+      </c>
+      <c r="B312" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A313">
+        <v>111240</v>
+      </c>
+      <c r="B313" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A314">
+        <v>111243</v>
+      </c>
+      <c r="B314" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A315">
+        <v>3274</v>
+      </c>
+      <c r="B315" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A316">
+        <v>3489</v>
+      </c>
+      <c r="B316" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A317">
+        <v>4123</v>
+      </c>
+      <c r="B317" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A318">
+        <v>4124</v>
+      </c>
+      <c r="B318" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A319">
+        <v>4374</v>
+      </c>
+      <c r="B319" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A320">
+        <v>4400</v>
+      </c>
+      <c r="B320" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A321">
+        <v>4435</v>
+      </c>
+      <c r="B321" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A322">
+        <v>4649</v>
+      </c>
+      <c r="B322" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A323">
+        <v>4773</v>
+      </c>
+      <c r="B323" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A324">
+        <v>4849</v>
+      </c>
+      <c r="B324" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A325">
+        <v>5042</v>
+      </c>
+      <c r="B325" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A326">
+        <v>5318</v>
+      </c>
+      <c r="B326" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A327">
+        <v>5329</v>
+      </c>
+      <c r="B327" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A328">
+        <v>5360</v>
+      </c>
+      <c r="B328" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A329">
+        <v>5396</v>
+      </c>
+      <c r="B329" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A330">
+        <v>5411</v>
+      </c>
+      <c r="B330" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A331">
+        <v>5455</v>
+      </c>
+      <c r="B331" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A332" t="s">
+        <v>8</v>
+      </c>
+      <c r="B332" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A333">
+        <v>5625</v>
+      </c>
+      <c r="B333" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A334">
+        <v>5630</v>
+      </c>
+      <c r="B334" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A335">
+        <v>5663</v>
+      </c>
+      <c r="B335" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A336">
+        <v>6002</v>
+      </c>
+      <c r="B336" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A337">
+        <v>6068</v>
+      </c>
+      <c r="B337" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A338">
+        <v>6077</v>
+      </c>
+      <c r="B338" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A339">
+        <v>6271</v>
+      </c>
+      <c r="B339" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A340">
+        <v>6274</v>
+      </c>
+      <c r="B340" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A341">
+        <v>6279</v>
+      </c>
+      <c r="B341" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A342">
+        <v>6286</v>
+      </c>
+      <c r="B342" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A343">
+        <v>6299</v>
+      </c>
+      <c r="B343" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A344">
+        <v>6322</v>
+      </c>
+      <c r="B344" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A345">
+        <v>6326</v>
+      </c>
+      <c r="B345" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A346">
+        <v>6350</v>
+      </c>
+      <c r="B346" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A347">
+        <v>6370</v>
+      </c>
+      <c r="B347" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A348">
+        <v>6548</v>
+      </c>
+      <c r="B348" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A349">
+        <v>6581</v>
+      </c>
+      <c r="B349" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A350">
+        <v>11321</v>
+      </c>
+      <c r="B350" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A351">
+        <v>11506</v>
+      </c>
+      <c r="B351" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A352">
+        <v>11978</v>
+      </c>
+      <c r="B352" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A353">
+        <v>12085</v>
+      </c>
+      <c r="B353" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A354">
+        <v>12219</v>
+      </c>
+      <c r="B354" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A355">
+        <v>12342</v>
+      </c>
+      <c r="B355" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A356">
+        <v>12506</v>
+      </c>
+      <c r="B356" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A357">
+        <v>12529</v>
+      </c>
+      <c r="B357" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A358">
+        <v>12894</v>
+      </c>
+      <c r="B358" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A359">
+        <v>12915</v>
+      </c>
+      <c r="B359" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A360">
+        <v>12942</v>
+      </c>
+      <c r="B360" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A361">
+        <v>111227</v>
+      </c>
+      <c r="B361" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A362">
+        <v>111462</v>
+      </c>
+      <c r="B362" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A363">
+        <v>111644</v>
+      </c>
+      <c r="B363" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A364">
+        <v>111686</v>
+      </c>
+      <c r="B364" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A365">
+        <v>111692</v>
+      </c>
+      <c r="B365" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A366">
+        <v>111865</v>
+      </c>
+      <c r="B366" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A367">
+        <v>4354</v>
+      </c>
+      <c r="B367" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A368">
+        <v>4423</v>
+      </c>
+      <c r="B368" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A369">
+        <v>4439</v>
+      </c>
+      <c r="B369" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A370">
+        <v>4791</v>
+      </c>
+      <c r="B370" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A371">
+        <v>4981</v>
+      </c>
+      <c r="B371" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A372">
+        <v>5031</v>
+      </c>
+      <c r="B372" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A373">
+        <v>5195</v>
+      </c>
+      <c r="B373" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A374">
+        <v>5239</v>
+      </c>
+      <c r="B374" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A375">
+        <v>5259</v>
+      </c>
+      <c r="B375" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A376">
+        <v>5296</v>
+      </c>
+      <c r="B376" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A377">
+        <v>5390</v>
+      </c>
+      <c r="B377" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A378">
+        <v>5456</v>
+      </c>
+      <c r="B378" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A379">
+        <v>5475</v>
+      </c>
+      <c r="B379" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A380">
+        <v>5622</v>
+      </c>
+      <c r="B380" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A381">
+        <v>5636</v>
+      </c>
+      <c r="B381" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A382">
+        <v>5735</v>
+      </c>
+      <c r="B382" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A383">
+        <v>5736</v>
+      </c>
+      <c r="B383" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A384">
+        <v>5786</v>
+      </c>
+      <c r="B384" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A385">
+        <v>5902</v>
+      </c>
+      <c r="B385" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A386">
+        <v>5960</v>
+      </c>
+      <c r="B386" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A387">
+        <v>5981</v>
+      </c>
+      <c r="B387" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A388">
+        <v>6043</v>
+      </c>
+      <c r="B388" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A389">
+        <v>6079</v>
+      </c>
+      <c r="B389" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A390">
+        <v>6222</v>
+      </c>
+      <c r="B390" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A391">
+        <v>6323</v>
+      </c>
+      <c r="B391" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A392">
+        <v>6330</v>
+      </c>
+      <c r="B392" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A393">
+        <v>6515</v>
+      </c>
+      <c r="B393" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A394">
+        <v>6522</v>
+      </c>
+      <c r="B394" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A395">
+        <v>6586</v>
+      </c>
+      <c r="B395" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A396">
+        <v>11082</v>
+      </c>
+      <c r="B396" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A397">
+        <v>11280</v>
+      </c>
+      <c r="B397" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A398">
+        <v>12476</v>
+      </c>
+      <c r="B398" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A399">
+        <v>12764</v>
+      </c>
+      <c r="B399" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A400">
+        <v>12770</v>
+      </c>
+      <c r="B400" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A401">
+        <v>12860</v>
+      </c>
+      <c r="B401" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A402">
+        <v>12956</v>
+      </c>
+      <c r="B402" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A403">
+        <v>12977</v>
+      </c>
+      <c r="B403" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A404">
+        <v>111184</v>
+      </c>
+      <c r="B404" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A405">
+        <v>111201</v>
+      </c>
+      <c r="B405" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A406">
+        <v>111325</v>
+      </c>
+      <c r="B406" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A407">
+        <v>111580</v>
+      </c>
+      <c r="B407" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A408">
+        <v>111697</v>
+      </c>
+      <c r="B408" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A409">
+        <v>111758</v>
+      </c>
+      <c r="B409" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
